--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -19667,12 +19667,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -19697,90 +19697,109 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>0.1401732064242502</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19807,17 +19826,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -19842,31 +19861,48 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O107" t="n">
-        <v>3</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0.05336427512592412</v>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Yersiniainfektion</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -19874,6 +19910,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN107" t="b">
+        <v>1</v>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -19886,7 +19980,7 @@
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
@@ -19896,7 +19990,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -19904,47 +19998,47 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19971,17 +20065,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -20015,175 +20109,81 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>3</v>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>Yersinia, total</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD108" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
+      <c r="AT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE108" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG108" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN108" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP108" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="AT108" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV108" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20215,12 +20215,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -20254,13 +20254,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -20289,7 +20289,7 @@
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT109" t="n">
@@ -20307,47 +20307,47 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20379,12 +20379,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -20418,29 +20418,29 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>Yersiniose</t>
+          <t>Yersinia, total</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
@@ -20465,7 +20465,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr">
@@ -20500,17 +20500,17 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -20528,7 +20528,7 @@
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
@@ -20538,7 +20538,7 @@
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT110" t="n">
@@ -20546,45 +20546,448 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV110" t="inlineStr">
+      <c r="AV111" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW110" t="inlineStr">
+      <c r="AW111" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
+      <c r="AX111" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY110" t="inlineStr">
+      <c r="AY111" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
+      <c r="AZ111" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA110" t="inlineStr">
+      <c r="BA111" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB110" t="inlineStr">
+      <c r="BB111" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC110" t="inlineStr">
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Yersiniose</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN112" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -20706,7 +21109,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -20716,7 +21119,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">
@@ -20736,7 +21139,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -20768,7 +21171,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1269</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -20254,13 +20254,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R109" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -20418,10 +20418,10 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -20657,13 +20657,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -20821,10 +20821,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -20254,13 +20254,13 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O109" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R109" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -20418,10 +20418,10 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U110" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -7490,10 +7490,10 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -12744,10 +12744,10 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -12900,10 +12900,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -15978,12 +15978,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -16017,22 +16017,19 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="O85" t="n">
-        <v>49</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0.8716164937234273</v>
+        <v>14</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -16047,70 +16044,65 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16142,12 +16134,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -16181,29 +16173,29 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="O86" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Yersinia, total</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -16213,7 +16205,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -16228,7 +16220,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr">
@@ -16263,17 +16255,17 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
+          <t>PHO IDTO current-year monthly preliminary yersiniosis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -16286,70 +16278,65 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16381,12 +16368,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -16420,13 +16407,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="O87" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="R87" t="n">
-        <v>0.1945873408375057</v>
+        <v>0.8716164937234273</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -16435,7 +16422,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -16455,7 +16442,7 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -16465,7 +16452,7 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -16473,47 +16460,47 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16545,12 +16532,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -16584,29 +16571,29 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="O88" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Yersiniose</t>
+          <t>Yersinia, total</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -16631,7 +16618,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
@@ -16666,17 +16653,17 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -16694,7 +16681,7 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
@@ -16704,7 +16691,7 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT88" t="n">
@@ -16712,47 +16699,47 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16784,12 +16771,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -16823,13 +16810,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="O89" t="n">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="R89" t="n">
-        <v>1.494095768512745</v>
+        <v>0.1945873408375057</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16838,7 +16825,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -16853,7 +16840,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
@@ -16861,57 +16848,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16943,12 +16935,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -16982,29 +16974,29 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="O90" t="n">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Yersiniose</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
@@ -17014,7 +17006,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -17029,7 +17021,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
@@ -17064,17 +17056,17 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly yersiniosis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -17087,7 +17079,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
@@ -17095,57 +17087,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17177,12 +17174,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -17216,13 +17213,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="O91" t="n">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="R91" t="n">
-        <v>0.1868976085656669</v>
+        <v>1.494095768512745</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -17231,7 +17228,7 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -17246,7 +17243,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
@@ -17254,62 +17251,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17341,12 +17333,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -17380,29 +17372,29 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="O92" t="n">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Yersiniainfektion</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
@@ -17412,7 +17404,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -17427,7 +17419,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr">
@@ -17462,17 +17454,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+          <t>New Zealand PHF Science monthly yersiniosis notifications.</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -17485,7 +17477,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
@@ -17493,62 +17485,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17580,12 +17567,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -17610,90 +17597,109 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>0.1868976085656669</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17720,17 +17726,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -17755,87 +17761,184 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Yersiniainfektion</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN94" t="b">
+        <v>1</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17867,12 +17970,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -17911,9 +18014,12 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -17947,12 +18053,12 @@
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -17967,12 +18073,12 @@
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
@@ -18009,12 +18115,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -18089,7 +18195,7 @@
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
@@ -18109,7 +18215,7 @@
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
@@ -18151,12 +18257,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -18231,7 +18337,7 @@
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
@@ -18251,7 +18357,7 @@
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
@@ -18293,12 +18399,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -18373,7 +18479,7 @@
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
@@ -18393,7 +18499,7 @@
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
@@ -18435,12 +18541,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -18515,7 +18621,7 @@
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
@@ -18535,7 +18641,7 @@
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
@@ -18577,12 +18683,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -18657,7 +18763,7 @@
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
@@ -18677,7 +18783,7 @@
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
@@ -18719,12 +18825,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -18799,7 +18905,7 @@
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
@@ -18819,7 +18925,7 @@
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
@@ -18861,12 +18967,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -18900,100 +19006,78 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>32</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0.569218934676524</v>
+        <v>0</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19020,17 +19104,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -19064,175 +19148,78 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>32</v>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>Yersinia, total</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD103" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE103" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF103" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG103" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN103" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP103" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="AT103" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV103" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19264,12 +19251,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -19303,13 +19290,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="O104" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="R104" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.569218934676524</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -19318,7 +19305,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -19338,7 +19325,7 @@
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
@@ -19348,7 +19335,7 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT104" t="n">
@@ -19356,47 +19343,47 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -19428,12 +19415,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -19467,29 +19454,29 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="O105" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>Yersiniose</t>
+          <t>Yersinia, total</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -19514,7 +19501,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
@@ -19549,17 +19536,17 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -19577,7 +19564,7 @@
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
@@ -19587,7 +19574,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT105" t="n">
@@ -19595,47 +19582,47 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -19667,12 +19654,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -19706,13 +19693,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O106" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="R106" t="n">
-        <v>0.1401732064242502</v>
+        <v>0.1061385495477304</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -19721,7 +19708,7 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -19751,7 +19738,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -19764,42 +19751,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -19831,12 +19818,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -19870,29 +19857,29 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O107" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>Yersiniainfektion</t>
+          <t>Yersiniose</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -19917,7 +19904,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -19952,17 +19939,17 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -19990,7 +19977,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -20003,42 +19990,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20070,12 +20057,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -20100,90 +20087,109 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>0.1401732064242502</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20210,17 +20216,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -20245,31 +20251,48 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O109" t="n">
-        <v>6</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0.1067285502518482</v>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Yersiniainfektion</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -20277,6 +20300,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN109" t="b">
+        <v>1</v>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -20289,7 +20370,7 @@
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
@@ -20299,7 +20380,7 @@
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT109" t="n">
@@ -20307,47 +20388,47 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20374,17 +20455,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -20418,175 +20499,81 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>6</v>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>Yersinia, total</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD110" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
+      <c r="AT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE110" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG110" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN110" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP110" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="AT110" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV110" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20618,12 +20605,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -20657,13 +20644,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O111" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R111" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -20672,7 +20659,7 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -20692,7 +20679,7 @@
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR111" t="inlineStr">
@@ -20702,7 +20689,7 @@
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT111" t="n">
@@ -20710,47 +20697,47 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20782,12 +20769,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -20821,29 +20808,29 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O112" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>Yersiniose</t>
+          <t>Yersinia, total</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
@@ -20868,7 +20855,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr">
@@ -20903,17 +20890,17 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -20931,7 +20918,7 @@
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
@@ -20941,7 +20928,7 @@
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT112" t="n">
@@ -20949,45 +20936,448 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" t="n">
+        <v>1</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV112" t="inlineStr">
+      <c r="AV113" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW112" t="inlineStr">
+      <c r="AW113" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
+      <c r="AX113" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY112" t="inlineStr">
+      <c r="AY113" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
+      <c r="AZ113" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA112" t="inlineStr">
+      <c r="BA113" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB112" t="inlineStr">
+      <c r="BB113" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC112" t="inlineStr">
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>1</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Yersiniose</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN114" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -21109,7 +21499,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -21119,7 +21509,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
@@ -21139,7 +21529,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -21171,7 +21561,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1288</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -19290,13 +19290,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O104" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R104" t="n">
-        <v>0.569218934676524</v>
+        <v>0.5870070263851653</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -19454,10 +19454,10 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O105" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -20644,13 +20644,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O111" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R111" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -20808,10 +20808,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O112" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1305</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -20057,12 +20057,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -20096,13 +20096,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="O108" t="n">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="R108" t="n">
-        <v>0.1401732064242502</v>
+        <v>2.004736094460139</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -20126,7 +20126,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
@@ -20134,62 +20134,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20221,12 +20216,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -20260,29 +20255,29 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="O109" t="n">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>Yersiniainfektion</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -20292,7 +20287,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -20307,7 +20302,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr">
@@ -20342,17 +20337,17 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+          <t>New Zealand PHF Science monthly yersiniosis notifications.</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -20365,7 +20360,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
@@ -20373,62 +20368,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20460,12 +20450,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -20490,90 +20480,109 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>0.1401732064242502</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20600,17 +20609,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -20635,31 +20644,48 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O111" t="n">
-        <v>12</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0.2134571005036965</v>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Yersiniainfektion</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -20667,6 +20693,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN111" t="b">
+        <v>1</v>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -20679,7 +20763,7 @@
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR111" t="inlineStr">
@@ -20689,7 +20773,7 @@
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
         </is>
       </c>
       <c r="AT111" t="n">
@@ -20697,47 +20781,47 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20764,17 +20848,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -20808,175 +20892,81 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>12</v>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Yersinia, total</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP112" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="AT112" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV112" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21008,12 +20998,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -21047,13 +21037,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O113" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="R113" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -21062,7 +21052,7 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -21082,7 +21072,7 @@
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
@@ -21092,7 +21082,7 @@
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT113" t="n">
@@ -21100,47 +21090,47 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21172,12 +21162,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -21211,29 +21201,29 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>Yersiniose</t>
+          <t>Yersinia, total</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -21258,7 +21248,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -21293,17 +21283,17 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -21321,7 +21311,7 @@
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
@@ -21331,7 +21321,7 @@
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT114" t="n">
@@ -21339,45 +21329,448 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV114" t="inlineStr">
+      <c r="AV115" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW114" t="inlineStr">
+      <c r="AW115" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
+      <c r="AX115" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY114" t="inlineStr">
+      <c r="AY115" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
+      <c r="AZ115" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA114" t="inlineStr">
+      <c r="BA115" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB114" t="inlineStr">
+      <c r="BB115" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC114" t="inlineStr">
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Yersiniose</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN116" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -21499,7 +21892,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -21509,7 +21902,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
@@ -21529,7 +21922,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -21561,7 +21954,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1311</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -21440,13 +21440,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R115" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -21604,10 +21604,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1417</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -21037,13 +21037,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O113" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R113" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -21201,10 +21201,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O114" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -19693,13 +19693,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O106" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R106" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -19857,10 +19857,10 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -21037,13 +21037,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O113" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R113" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.3379737424641861</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -21201,10 +21201,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O114" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -21440,13 +21440,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R115" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -21604,10 +21604,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1420</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -21037,13 +21037,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O113" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R113" t="n">
-        <v>0.3379737424641861</v>
+        <v>0.426914201007393</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -21201,10 +21201,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O114" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -21773,6 +21773,409 @@
       <c r="BC116" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AT117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Yersinia, total</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AT118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21809,7 +22212,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -21892,7 +22295,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -21902,7 +22305,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -21922,7 +22325,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -21954,7 +22357,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1426</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -1957,7 +1957,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -19693,13 +19693,13 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O106" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R106" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -19857,10 +19857,10 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O107" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
@@ -19949,7 +19949,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21037,13 +21037,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O113" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R113" t="n">
-        <v>0.426914201007393</v>
+        <v>0.4624903844246757</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -21201,10 +21201,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O114" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -21440,13 +21440,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R115" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -21604,10 +21604,10 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -22357,7 +22357,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1431</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3117,7 +3162,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4079,6 +4124,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4224,6 +4274,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4369,6 +4424,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4514,6 +4574,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4659,6 +4724,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4804,6 +4874,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4949,6 +5024,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5094,6 +5174,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5239,6 +5324,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6420,7 +6510,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7382,6 +7472,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7527,6 +7622,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7672,6 +7772,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7817,6 +7922,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7962,6 +8072,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8107,6 +8222,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8252,6 +8372,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8397,6 +8522,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8542,6 +8672,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9723,7 +9858,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -10682,6 +10817,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10827,6 +10967,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10972,6 +11117,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11117,6 +11267,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11262,6 +11417,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11407,6 +11567,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11552,6 +11717,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11697,6 +11867,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11842,6 +12017,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13023,7 +13203,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -13979,6 +14159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14124,6 +14309,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14269,6 +14459,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14414,6 +14609,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14559,6 +14759,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14704,6 +14909,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14849,6 +15059,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14994,6 +15209,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15139,6 +15359,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16320,7 +16545,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -17276,6 +17501,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17421,6 +17651,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17566,6 +17801,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17711,6 +17951,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17856,6 +18101,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18001,6 +18251,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18146,6 +18401,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18291,6 +18551,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18436,6 +18701,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19617,7 +19887,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -20573,6 +20843,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20718,6 +20993,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20863,6 +21143,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21008,6 +21293,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21153,6 +21443,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21298,6 +21593,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21443,6 +21743,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21588,6 +21893,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21733,6 +22043,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22914,7 +23229,7 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -23870,6 +24185,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24015,6 +24335,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24160,6 +24485,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24305,6 +24635,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24450,6 +24785,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24595,6 +24935,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24740,6 +25085,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24885,6 +25235,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25030,6 +25385,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25123,12 +25483,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -25162,22 +25522,19 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="O144" t="n">
-        <v>33</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0.5870070263851653</v>
+        <v>19</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -25192,70 +25549,65 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ144" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25287,12 +25639,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -25326,29 +25678,29 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="O145" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>Yersinia, total</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -25358,7 +25710,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -25373,7 +25725,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -25408,17 +25760,17 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
+          <t>PHO IDTO current-year monthly preliminary yersiniosis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -25431,70 +25783,65 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_CA_ON_PHO_IDTO_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25526,12 +25873,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -25565,13 +25912,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="O146" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="R146" t="n">
-        <v>0.1592078243215956</v>
+        <v>0.5870070263851653</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -25580,7 +25927,7 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -25600,7 +25947,7 @@
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
@@ -25610,7 +25957,7 @@
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT146" t="n">
@@ -25618,47 +25965,47 @@
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25690,12 +26037,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25729,29 +26076,29 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="O147" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>Yersiniose</t>
+          <t>Yersinia, total</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -25776,7 +26123,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
@@ -25811,17 +26158,17 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -25839,7 +26186,7 @@
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
@@ -25849,7 +26196,7 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT147" t="n">
@@ -25857,47 +26204,47 @@
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25929,12 +26276,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -25968,13 +26315,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="O148" t="n">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="R148" t="n">
-        <v>2.004736094460139</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -25983,7 +26330,7 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -25998,7 +26345,7 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
@@ -26006,57 +26353,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26088,12 +26440,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -26127,29 +26479,29 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="O149" t="n">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>Yersiniosis</t>
+          <t>Yersiniose</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -26159,7 +26511,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -26174,7 +26526,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
@@ -26209,17 +26561,17 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly yersiniosis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -26232,7 +26584,7 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
@@ -26240,57 +26592,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26322,12 +26679,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -26361,13 +26718,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="O150" t="n">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="R150" t="n">
-        <v>0.1401732064242502</v>
+        <v>2.004736094460139</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -26376,7 +26733,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -26391,7 +26748,7 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
@@ -26399,62 +26756,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26486,12 +26838,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -26525,29 +26877,29 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="O151" t="n">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>Yersiniainfektion</t>
+          <t>Yersiniosis</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
@@ -26557,7 +26909,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -26572,7 +26924,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -26607,17 +26959,17 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+          <t>New Zealand PHF Science monthly yersiniosis notifications.</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -26630,7 +26982,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
@@ -26638,62 +26990,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+          <t>SER_NZ_YERSINIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26725,12 +27072,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26755,90 +27102,109 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>0.1401732064242502</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26865,17 +27231,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26900,90 +27266,184 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O153" t="n">
-        <v>0</v>
-      </c>
-      <c r="R153" t="n">
-        <v>0</v>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Yersiniainfektion</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
       <c r="AT153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27015,12 +27475,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -27064,7 +27524,12 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -27098,12 +27563,12 @@
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -27118,12 +27583,12 @@
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
@@ -27160,12 +27625,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -27210,6 +27675,11 @@
       <c r="S155" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -27243,7 +27713,7 @@
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
@@ -27263,7 +27733,7 @@
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
@@ -27305,12 +27775,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -27355,6 +27825,11 @@
       <c r="S156" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -27388,7 +27863,7 @@
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
@@ -27408,7 +27883,7 @@
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
@@ -27450,12 +27925,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -27500,6 +27975,11 @@
       <c r="S157" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -27533,7 +28013,7 @@
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
@@ -27553,7 +28033,7 @@
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
@@ -27595,12 +28075,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27645,6 +28125,11 @@
       <c r="S158" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -27678,7 +28163,7 @@
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
@@ -27698,7 +28183,7 @@
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
@@ -27740,12 +28225,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27790,6 +28275,11 @@
       <c r="S159" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -27823,7 +28313,7 @@
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
@@ -27843,7 +28333,7 @@
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
@@ -27885,12 +28375,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27935,6 +28425,11 @@
       <c r="S160" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -27968,7 +28463,7 @@
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
@@ -27988,7 +28483,7 @@
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
@@ -28030,12 +28525,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -28069,22 +28564,17 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>0.4624903844246757</v>
+        <v>0</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -28094,75 +28584,66 @@
       </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR161" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28189,17 +28670,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -28233,39 +28714,17 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>26</v>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Yersinia, total</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -28273,135 +28732,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP162" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1220</t>
-        </is>
-      </c>
-      <c r="AT162" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV162" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28433,12 +28825,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -28472,13 +28864,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="O163" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="R163" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.4980665678419585</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -28487,7 +28879,7 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -28507,7 +28899,7 @@
       </c>
       <c r="AQ163" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR163" t="inlineStr">
@@ -28517,7 +28909,7 @@
       </c>
       <c r="AS163" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT163" t="n">
@@ -28525,47 +28917,47 @@
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28597,12 +28989,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -28636,29 +29028,29 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="O164" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>Yersiniose</t>
+          <t>Yersinia, total</t>
         </is>
       </c>
       <c r="Y164" t="inlineStr">
@@ -28683,7 +29075,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD164" t="inlineStr">
@@ -28718,17 +29110,17 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -28746,7 +29138,7 @@
       </c>
       <c r="AQ164" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR164" t="inlineStr">
@@ -28756,7 +29148,7 @@
       </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_303_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1220</t>
         </is>
       </c>
       <c r="AT164" t="n">
@@ -28764,47 +29156,47 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28836,12 +29228,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28866,22 +29258,22 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -28890,7 +29282,7 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -28910,7 +29302,7 @@
       </c>
       <c r="AQ165" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR165" t="inlineStr">
@@ -28920,7 +29312,7 @@
       </c>
       <c r="AS165" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT165" t="n">
@@ -28928,47 +29320,47 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -29000,12 +29392,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -29030,38 +29422,38 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O166" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="V166" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>Yersinia, total</t>
+          <t>Yersiniose</t>
         </is>
       </c>
       <c r="Y166" t="inlineStr">
@@ -29086,7 +29478,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD166" t="inlineStr">
@@ -29121,17 +29513,17 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -29149,7 +29541,7 @@
       </c>
       <c r="AQ166" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
@@ -29159,7 +29551,7 @@
       </c>
       <c r="AS166" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1220</t>
+          <t>SER_NO_FHI_303_MONTHLY</t>
         </is>
       </c>
       <c r="AT166" t="n">
@@ -29167,47 +29559,1256 @@
       </c>
       <c r="AU166" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>15</v>
+      </c>
+      <c r="O167" t="n">
+        <v>15</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.1401732064242502</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="AT167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>15</v>
+      </c>
+      <c r="O168" t="n">
+        <v>15</v>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>Yersiniainfektion</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Yersinia category.</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN168" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_YERSINIA</t>
+        </is>
+      </c>
+      <c r="AT168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>2</v>
+      </c>
+      <c r="O169" t="n">
+        <v>2</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0.03557618341728275</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AT169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV166" t="inlineStr">
+      <c r="AV169" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW166" t="inlineStr">
+      <c r="AW169" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX166" t="inlineStr">
+      <c r="AX169" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY166" t="inlineStr">
+      <c r="AY169" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ166" t="inlineStr">
+      <c r="AZ169" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA166" t="inlineStr">
+      <c r="BA169" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB166" t="inlineStr">
+      <c r="BB169" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC166" t="inlineStr">
+      <c r="BC169" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>2</v>
+      </c>
+      <c r="O170" t="n">
+        <v>2</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Yersinia, total</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total; species child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN170" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1220</t>
+        </is>
+      </c>
+      <c r="AT170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>yersiniosis</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D155</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Yersiniosis</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>耶尔森菌病</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Yersiniose</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN172" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_303_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -29327,7 +30928,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -29337,7 +30938,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -29357,7 +30958,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -29389,7 +30990,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1436</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -27111,13 +27111,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O152" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R152" t="n">
-        <v>0.1401732064242502</v>
+        <v>0.1214834455676835</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -27275,10 +27275,10 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O153" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
@@ -29267,13 +29267,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O165" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R165" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.1061385495477304</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -29431,10 +29431,10 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O166" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
@@ -29670,13 +29670,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O167" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R167" t="n">
-        <v>0.1401732064242502</v>
+        <v>0.1214834455676835</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -29834,10 +29834,10 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O168" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="U168" t="inlineStr">
         <is>
@@ -30476,13 +30476,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -30640,10 +30640,10 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>

--- a/diseases/d155/2026-2029.xlsx
+++ b/diseases/d155/2026-2029.xlsx
@@ -23769,13 +23769,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O133" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R133" t="n">
-        <v>0.1868976085656669</v>
+        <v>0.1682078477091002</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23933,10 +23933,10 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O134" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1474</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="16">
